--- a/backend/data/financials_by_company/0267.HK.xlsx
+++ b/backend/data/financials_by_company/0267.HK.xlsx
@@ -3291,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FK2"/>
+  <dimension ref="A1:FJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3967,165 +3967,160 @@
       </c>
       <c r="EE1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FG1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
       <c r="FJ1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FK1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4207,7 +4202,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Guohua  Xi Ph.D.', 'age': 62, 'title': 'Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1180669, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenwu  Zhang', 'age': 52, 'title': 'President &amp; Executive Vice Chairman', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 966273, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhengjun  Liu', 'age': 60, 'title': 'VP &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 1064917, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guoquan  Wang', 'age': 53, 'title': 'VP &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 1064917, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Huijiang', 'age': 55, 'title': 'Chief Investment Officer', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Xiaoyan  Liu', 'title': 'Accounting Supervisor', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chen Meng Holly', 'age': 58, 'title': 'Director of Group Investor Relations &amp; Corporate Communications', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Kay  Choy', 'age': 50, 'title': 'Group General Counsel &amp; Joint Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Youjun  Zhang', 'age': 60, 'title': 'Assistant President', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shijun  Cheng', 'age': 60, 'title': 'Chief Auditor', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Guohua  Xi Ph.D.', 'age': 62, 'title': 'Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1177503, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenwu  Zhang', 'age': 52, 'title': 'President &amp; Executive Vice Chairman', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 963682, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhengjun  Liu', 'age': 60, 'title': 'VP &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 1062061, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guoquan  Wang', 'age': 53, 'title': 'VP &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 1062061, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Huijiang', 'age': 55, 'title': 'Chief Investment Officer', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Xiaoyan  Liu', 'title': 'Accounting Supervisor', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chen Meng Holly', 'age': 58, 'title': 'Director of Group Investor Relations &amp; Corporate Communications', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Kay  Choy', 'age': 50, 'title': 'Group General Counsel &amp; Joint Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Youjun  Zhang', 'age': 60, 'title': 'Assistant President', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shijun  Cheng', 'age': 60, 'title': 'Chief Auditor', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4220,13 +4215,13 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>1780531200</v>
+        <v>1782864000</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -4248,34 +4243,34 @@
         <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.4</v>
+        <v>10.69</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.41</v>
+        <v>10.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.9</v>
+        <v>10.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>12.43</v>
+        <v>10.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.4</v>
+        <v>10.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.41</v>
+        <v>10.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>11.9</v>
+        <v>10.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>12.43</v>
+        <v>10.85</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.66</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.34</v>
+        <v>6.19</v>
       </c>
       <c r="AL2" t="n">
         <v>1782777600</v>
@@ -4284,37 +4279,37 @@
         <v>0.27899998</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.862</v>
+        <v>0.863</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.2789702</v>
+        <v>4.6422415</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.884189</v>
+        <v>4.2766438</v>
       </c>
       <c r="AR2" t="n">
-        <v>36069428</v>
+        <v>20088951</v>
       </c>
       <c r="AS2" t="n">
-        <v>36069428</v>
+        <v>20088951</v>
       </c>
       <c r="AT2" t="n">
-        <v>22684415</v>
+        <v>24378255</v>
       </c>
       <c r="AU2" t="n">
-        <v>37955655</v>
+        <v>33246101</v>
       </c>
       <c r="AV2" t="n">
-        <v>37955655</v>
+        <v>33246101</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.28</v>
+        <v>10.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.3</v>
+        <v>10.72</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4323,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>357810241536</v>
+        <v>313302155264</v>
       </c>
       <c r="BB2" t="n">
-        <v>360719256612</v>
+        <v>310974907514</v>
       </c>
       <c r="BC2" t="n">
-        <v>10.46</v>
+        <v>10.42</v>
       </c>
       <c r="BD2" t="n">
         <v>13.9</v>
@@ -4341,19 +4336,19 @@
         <v>3.66</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.37856707</v>
+        <v>0.33147705</v>
       </c>
       <c r="BH2" t="n">
-        <v>13.1252</v>
+        <v>12.9366</v>
       </c>
       <c r="BI2" t="n">
-        <v>12.28915</v>
+        <v>12.2664</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.585</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.04717742</v>
+        <v>0.05472404</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -4364,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1937603166208</v>
+        <v>1893095178240</v>
       </c>
       <c r="BO2" t="n">
         <v>0.062140003</v>
@@ -4379,16 +4374,16 @@
         <v>0.73121</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.13832</v>
+        <v>0.13891</v>
       </c>
       <c r="BT2" t="n">
         <v>29090262630</v>
       </c>
       <c r="BU2" t="n">
-        <v>31.130537</v>
+        <v>31.046824</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.39511043</v>
+        <v>0.3468954</v>
       </c>
       <c r="BW2" t="n">
         <v>1767139200</v>
@@ -4406,7 +4401,7 @@
         <v>58730000384</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CC2" t="n">
         <v>2.51833</v>
@@ -4415,19 +4410,19 @@
         <v>1.76</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.05</v>
+        <v>2.003</v>
       </c>
       <c r="CF2" t="n">
-        <v>5.99</v>
+        <v>5.852</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.097345114</v>
+        <v>0.00093638897</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.385</v>
+        <v>0.442696</v>
       </c>
       <c r="CJ2" t="n">
         <v>1782777600</v>
@@ -4438,7 +4433,7 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>12.3</v>
+        <v>10.77</v>
       </c>
       <c r="CM2" t="n">
         <v>14.8</v>
@@ -4557,11 +4552,11 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>[{'header': 'Dividend', 'message': '0267.HK announced a cash dividend of HKD 0.385 with an ex-date of Jun. 30, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1782748800000, 'amount': '0.385'}}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="DU2" t="n">
-        <v>1782115692</v>
+        <v>1783066093</v>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
@@ -4595,120 +4590,117 @@
         <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0.806447</v>
+        <v>0.7483712</v>
       </c>
       <c r="ED2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="EE2" t="b">
+        <v>10.77</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>CITIC</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>CITIC Limited</t>
+        </is>
+      </c>
+      <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EH2" t="n">
+        <v>0.08000088</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>10.62 - 10.85</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EK2" t="n">
+        <v>24378255</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.35000038</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.03358929</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>10.42 - 13.9</t>
+        </is>
+      </c>
+      <c r="EO2" t="n">
+        <v>-3.1299992</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.2251798</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0.0936389</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1774599000</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>1774599000</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1743145200</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1743145200</v>
+      </c>
+      <c r="EV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>2.51833</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>2.40333</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>4.481282</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>-2.1665993</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>-0.16747826</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>-1.4963999</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>-0.12199177</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="FH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FI2" t="n">
         <v>946949400000</v>
       </c>
-      <c r="EG2" t="n">
-        <v>-0.09999943</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>11.9 - 12.43</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>CITIC</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>CITIC Limited</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>5.117899</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.8252001</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.06287143000000001</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.010849953</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.0008828888</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EU2" t="n">
-        <v>22684415</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1.8400002</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>0.17590824</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>10.46 - 13.9</t>
-        </is>
-      </c>
-      <c r="EY2" t="n">
-        <v>-1.5999994</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>-0.11510788</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>9.734510999999999</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1774599000</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>1774599000</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1774599000</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>1743145200</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>1743145200</v>
-      </c>
-      <c r="FG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>2.51833</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>2.40333</v>
-      </c>
-      <c r="FK2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
